--- a/data/trans_orig/P23_1_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89292</t>
+          <t>88679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123890</t>
+          <t>124050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141631</t>
+          <t>143183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174394</t>
+          <t>177593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239536</t>
+          <t>240308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291220</t>
+          <t>291676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66002</t>
+          <t>65354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97611</t>
+          <t>97278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70671</t>
+          <t>68685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115162</t>
+          <t>113570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156367</t>
+          <t>156029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79977</t>
+          <t>81532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115183</t>
+          <t>116061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81162</t>
+          <t>80028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139324</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183212</t>
+          <t>186210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>185556</t>
+          <t>186113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230974</t>
+          <t>229506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>315602</t>
+          <t>317994</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>361142</t>
+          <t>362489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>514641</t>
+          <t>518218</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>583891</t>
+          <t>582390</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68971</t>
+          <t>69477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103430</t>
+          <t>103827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52927</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>144932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173463</t>
+          <t>169021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218349</t>
+          <t>215071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116180</t>
+          <t>114401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158087</t>
+          <t>156792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>300920</t>
+          <t>302524</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>364692</t>
+          <t>359957</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134780</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169487</t>
+          <t>170109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206940</t>
+          <t>206365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240414</t>
+          <t>240724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>351413</t>
+          <t>351995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401415</t>
+          <t>400913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>84395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83215</t>
+          <t>83321</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119849</t>
+          <t>119078</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73011</t>
+          <t>73949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103066</t>
+          <t>106609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61130</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91577</t>
+          <t>91754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142557</t>
+          <t>143409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186315</t>
+          <t>186373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111547</t>
+          <t>112467</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>151377</t>
+          <t>150511</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206156</t>
+          <t>206854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245270</t>
+          <t>247618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>327639</t>
+          <t>332371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>386976</t>
+          <t>386993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83028</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117735</t>
+          <t>115904</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128185</t>
+          <t>127849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>173507</t>
+          <t>173683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>16739</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>32928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113946</t>
+          <t>113294</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153172</t>
+          <t>152029</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114983</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201880</t>
+          <t>199205</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251915</t>
+          <t>252708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>67907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96575</t>
+          <t>94964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125987</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>152506</t>
+          <t>154015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>201315</t>
+          <t>200079</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241749</t>
+          <t>241819</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33784</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54344</t>
+          <t>52100</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83790</t>
+          <t>83171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66306</t>
+          <t>66456</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95685</t>
+          <t>94130</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>118165</t>
+          <t>117804</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>157672</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107446</t>
+          <t>107464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138864</t>
+          <t>138687</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>167301</t>
+          <t>166695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>197907</t>
+          <t>196765</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>284782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>329227</t>
+          <t>327903</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39793</t>
+          <t>39964</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65066</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53596</t>
+          <t>54619</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83075</t>
+          <t>84129</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>69278</t>
+          <t>69997</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100961</t>
+          <t>100244</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51587</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>130062</t>
+          <t>129775</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170655</t>
+          <t>170266</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>299684</t>
+          <t>297333</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>353824</t>
+          <t>351346</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>403646</t>
+          <t>402350</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>456395</t>
+          <t>452970</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>715126</t>
+          <t>715964</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>788592</t>
+          <t>792268</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>110112</t>
+          <t>111469</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>157642</t>
+          <t>152842</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>71166</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>105026</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>189813</t>
+          <t>193381</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>245991</t>
+          <t>248705</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34615</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27452</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54585</t>
+          <t>53514</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>157619</t>
+          <t>157581</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>205862</t>
+          <t>203979</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>128283</t>
+          <t>129596</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>173392</t>
+          <t>172520</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>299065</t>
+          <t>299542</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>365222</t>
+          <t>365340</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>357023</t>
+          <t>353659</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>412295</t>
+          <t>413845</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>496664</t>
+          <t>495769</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>553574</t>
+          <t>552576</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>865828</t>
+          <t>868831</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>946314</t>
+          <t>947582</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,05%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>121065</t>
+          <t>119377</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>165344</t>
+          <t>168070</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>68268</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>109203</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200174</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>257675</t>
+          <t>257220</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>208837</t>
+          <t>208788</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>262760</t>
+          <t>262322</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>181320</t>
+          <t>181056</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>231796</t>
+          <t>229852</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>406290</t>
+          <t>404245</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>478113</t>
+          <t>476636</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1451376</t>
+          <t>1449245</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1566437</t>
+          <t>1566820</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2165439</t>
+          <t>2176920</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2285150</t>
+          <t>2290098</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3656461</t>
+          <t>3658622</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3824575</t>
+          <t>3832103</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>657993</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>752570</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1034000</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1154938</t>
+          <t>1154919</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>107230</t>
+          <t>105115</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>134015</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>185244</t>
+          <t>188696</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1033109</t>
+          <t>1033431</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1146631</t>
+          <t>1147404</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,12 +5637,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>796934</t>
+          <t>795476</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>900794</t>
+          <t>897454</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1858282</t>
+          <t>1860794</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2016034</t>
+          <t>2010892</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2023</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156284</t>
+          <t>159137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>199026</t>
+          <t>201118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200214</t>
+          <t>200068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223646</t>
+          <t>224202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>367966</t>
+          <t>365618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>416756</t>
+          <t>415479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>35596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61392</t>
+          <t>60566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>47470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72782</t>
+          <t>73603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>28647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56521</t>
+          <t>56048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91810</t>
+          <t>90934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49656</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72471</t>
+          <t>72031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114027</t>
+          <t>113108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155159</t>
+          <t>158206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245266</t>
+          <t>238032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>302048</t>
+          <t>299996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>330808</t>
+          <t>330054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>368557</t>
+          <t>367360</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>588126</t>
+          <t>586677</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>656605</t>
+          <t>655818</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92632</t>
+          <t>91072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134079</t>
+          <t>135099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80239</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153549</t>
+          <t>154456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202542</t>
+          <t>206532</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38978</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22809</t>
+          <t>23561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47314</t>
+          <t>48771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96251</t>
+          <t>94308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143360</t>
+          <t>143329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>72590</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102627</t>
+          <t>103948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175545</t>
+          <t>179510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>231304</t>
+          <t>235891</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154584</t>
+          <t>154412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188413</t>
+          <t>191528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219935</t>
+          <t>220430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249089</t>
+          <t>249417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384443</t>
+          <t>384350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>430720</t>
+          <t>432014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81833</t>
+          <t>82179</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62240</t>
+          <t>62009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101384</t>
+          <t>101875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136717</t>
+          <t>136768</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57794</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85689</t>
+          <t>85398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>48279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72390</t>
+          <t>71563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111668</t>
+          <t>112960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147070</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118029</t>
+          <t>118117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163626</t>
+          <t>163580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307613</t>
+          <t>307381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>397362</t>
+          <t>395826</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>434957</t>
+          <t>438072</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>566155</t>
+          <t>575518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78880</t>
+          <t>78211</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113968</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76438</t>
+          <t>77721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113917</t>
+          <t>111080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182768</t>
+          <t>182201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56392</t>
+          <t>56759</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96018</t>
+          <t>94243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40082</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>91141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103302</t>
+          <t>101947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173498</t>
+          <t>172233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119049</t>
+          <t>119986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>138418</t>
+          <t>138800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162761</t>
+          <t>162659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>177157</t>
+          <t>178082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>287447</t>
+          <t>286479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>312140</t>
+          <t>312088</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30266</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>41755</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>48672</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>68121</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>132568</t>
+          <t>133508</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>165217</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>186014</t>
+          <t>186447</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>207937</t>
+          <t>207762</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>328915</t>
+          <t>328195</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>365146</t>
+          <t>364889</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -9046,12 +9046,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45306</t>
+          <t>46876</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>70213</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9131,12 +9131,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9159,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>16894</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -9272,12 +9272,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>55540</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>83132</t>
+          <t>81810</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9287,12 +9287,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35424</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55234</t>
+          <t>55644</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9322,12 +9322,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>95982</t>
+          <t>96928</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>128224</t>
+          <t>129663</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>295511</t>
+          <t>295970</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>357035</t>
+          <t>356863</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>506637</t>
+          <t>509343</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>741410</t>
+          <t>732147</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>825092</t>
+          <t>821312</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1133793</t>
+          <t>1121744</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>103463</t>
+          <t>104130</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>144004</t>
+          <t>141819</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>43996</t>
+          <t>39596</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>134783</t>
+          <t>131943</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>135531</t>
+          <t>138258</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>262893</t>
+          <t>262808</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37353</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>30397</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>72453</t>
+          <t>72107</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>119233</t>
+          <t>121923</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>177659</t>
+          <t>176699</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>51267</t>
+          <t>63479</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>178593</t>
+          <t>178601</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>170045</t>
+          <t>174407</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>330267</t>
+          <t>332051</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -10071,12 +10071,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>174176</t>
+          <t>179355</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>548722</t>
+          <t>549917</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>540584</t>
+          <t>539372</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>578399</t>
+          <t>577655</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>579071</t>
+          <t>605592</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1137670</t>
+          <t>1132600</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10156,12 +10156,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -10184,12 +10184,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>132489</t>
+          <t>130443</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>669981</t>
+          <t>654262</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>48580</t>
+          <t>48420</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>158695</t>
+          <t>158441</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>872938</t>
+          <t>853817</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10269,12 +10269,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10332,12 +10332,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10347,12 +10347,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>17062</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -10410,12 +10410,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>81686</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>258052</t>
+          <t>259170</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10445,12 +10445,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>94838</t>
+          <t>93913</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128772</t>
+          <t>128233</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10480,12 +10480,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>183685</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>353158</t>
+          <t>353961</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -10640,12 +10640,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1387859</t>
+          <t>1312916</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1932155</t>
+          <t>1930270</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10655,12 +10655,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2579319</t>
+          <t>2577228</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2873419</t>
+          <t>2847425</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3913971</t>
+          <t>3958696</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4690388</t>
+          <t>4683345</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>637003</t>
+          <t>641386</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1404653</t>
+          <t>1477012</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>261388</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>377059</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10803,12 +10803,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10823,12 +10823,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>950224</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1975074</t>
+          <t>1829952</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10838,12 +10838,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>104919</t>
+          <t>103371</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>86583</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10916,12 +10916,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>112110</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>174954</t>
+          <t>177347</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10951,12 +10951,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -10979,12 +10979,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>613920</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>844674</t>
+          <t>838145</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10994,12 +10994,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11014,12 +11014,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>463952</t>
+          <t>483868</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>640144</t>
+          <t>643754</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11029,12 +11029,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11049,12 +11049,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1168029</t>
+          <t>1165792</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1454703</t>
+          <t>1459122</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11064,12 +11064,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88679</t>
+          <t>89451</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>123961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143183</t>
+          <t>142452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>178788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240308</t>
+          <t>241756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291676</t>
+          <t>290829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65354</t>
+          <t>64783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>95566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68685</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>116162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156029</t>
+          <t>157379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>28182</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81532</t>
+          <t>82015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116061</t>
+          <t>115651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>52013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80028</t>
+          <t>80506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141507</t>
+          <t>141666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186113</t>
+          <t>185303</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>229506</t>
+          <t>232391</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>317994</t>
+          <t>316904</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>362489</t>
+          <t>361538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>518218</t>
+          <t>516314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>582390</t>
+          <t>582852</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69477</t>
+          <t>69234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103827</t>
+          <t>105840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102093</t>
+          <t>104339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144932</t>
+          <t>148101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169021</t>
+          <t>173488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215071</t>
+          <t>216450</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>114401</t>
+          <t>116848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>155278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>299233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>359957</t>
+          <t>360862</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134949</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170109</t>
+          <t>171435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206365</t>
+          <t>207657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240724</t>
+          <t>241493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>351995</t>
+          <t>351903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>400913</t>
+          <t>400647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84395</t>
+          <t>87100</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40949</t>
+          <t>40137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83321</t>
+          <t>84482</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119078</t>
+          <t>118636</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73949</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106609</t>
+          <t>104069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>92217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143409</t>
+          <t>142825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186373</t>
+          <t>186202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112467</t>
+          <t>113351</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150511</t>
+          <t>149437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206854</t>
+          <t>203806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247618</t>
+          <t>243384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>332371</t>
+          <t>331178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>386993</t>
+          <t>391015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83422</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115904</t>
+          <t>117643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>38960</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64607</t>
+          <t>65592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127849</t>
+          <t>127585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>173683</t>
+          <t>170913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,47 +2714,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>21686</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>13626</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>31410</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>21686</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>13471</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>32928</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113294</t>
+          <t>113881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152029</t>
+          <t>149111</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78706</t>
+          <t>79289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114904</t>
+          <t>114462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>199205</t>
+          <t>199337</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252708</t>
+          <t>250995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>69055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94964</t>
+          <t>95848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126100</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154015</t>
+          <t>153496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200079</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241819</t>
+          <t>242614</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57805</t>
+          <t>56033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52100</t>
+          <t>52292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83171</t>
+          <t>81879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66456</t>
+          <t>66854</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>94130</t>
+          <t>94032</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>70083</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,47 +3396,47 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
+          <t>32,06%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>136504</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>119283</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>155512</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>31,76%</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>136504</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>117804</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>156476</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107464</t>
+          <t>107737</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138687</t>
+          <t>140454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>166695</t>
+          <t>166684</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>196765</t>
+          <t>197991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>284782</t>
+          <t>284581</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>327903</t>
+          <t>330646</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39964</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>65055</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>54837</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>84129</t>
+          <t>85524</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>68422</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100244</t>
+          <t>98080</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>129775</t>
+          <t>129902</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170266</t>
+          <t>172543</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>297333</t>
+          <t>297710</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>351346</t>
+          <t>353302</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>402350</t>
+          <t>404833</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>452970</t>
+          <t>456434</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>715964</t>
+          <t>721357</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>792268</t>
+          <t>793464</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,0%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>111469</t>
+          <t>110276</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>152842</t>
+          <t>154025</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>70005</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>105026</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>193381</t>
+          <t>192515</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>248705</t>
+          <t>252185</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27860</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>53514</t>
+          <t>55149</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>157581</t>
+          <t>156322</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>203979</t>
+          <t>204670</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>129596</t>
+          <t>129043</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>172520</t>
+          <t>172091</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>299542</t>
+          <t>298111</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>365340</t>
+          <t>363949</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>353659</t>
+          <t>355128</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>413845</t>
+          <t>412202</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>495769</t>
+          <t>495771</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>552576</t>
+          <t>554132</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>868831</t>
+          <t>866908</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>947582</t>
+          <t>945462</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>119377</t>
+          <t>119065</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>168070</t>
+          <t>163916</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>71270</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>109203</t>
+          <t>107494</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>200174</t>
+          <t>200081</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>257220</t>
+          <t>258074</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>208788</t>
+          <t>209569</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>262322</t>
+          <t>260980</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>181056</t>
+          <t>180391</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>229852</t>
+          <t>234066</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>404245</t>
+          <t>402404</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>476636</t>
+          <t>477461</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1449245</t>
+          <t>1454347</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1566820</t>
+          <t>1567651</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2176920</t>
+          <t>2166418</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2290098</t>
+          <t>2286805</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3658622</t>
+          <t>3660422</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3832103</t>
+          <t>3829403</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>657993</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>752729</t>
+          <t>749469</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1025856</t>
+          <t>1030338</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1154919</t>
+          <t>1155140</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>69222</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105992</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>137785</t>
+          <t>134654</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>188696</t>
+          <t>186034</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1033431</t>
+          <t>1043197</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1147404</t>
+          <t>1147034</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,12 +5637,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>795476</t>
+          <t>796790</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>897454</t>
+          <t>904834</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1860794</t>
+          <t>1860282</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2010892</t>
+          <t>2013913</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -6083,32 +6083,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>179549</t>
+          <t>192533</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159137</t>
+          <t>175306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201118</t>
+          <t>210989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6118,32 +6118,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>212517</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200068</t>
+          <t>223835</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>224202</t>
+          <t>248313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6153,32 +6153,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>392065</t>
+          <t>429825</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>365618</t>
+          <t>407050</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>415479</t>
+          <t>450620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -6196,32 +6196,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35596</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60566</t>
+          <t>64073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6266,32 +6266,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47470</t>
+          <t>50727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73603</t>
+          <t>77201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -6309,32 +6309,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6344,32 +6344,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6379,32 +6379,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33968</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -6422,32 +6422,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72676</t>
+          <t>65118</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56048</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90934</t>
+          <t>80527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60150</t>
+          <t>60258</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50345</t>
+          <t>51006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72031</t>
+          <t>72705</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6492,32 +6492,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132826</t>
+          <t>125376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>106674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158206</t>
+          <t>145040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -6535,17 +6535,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6652,32 +6652,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273389</t>
+          <t>274402</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238032</t>
+          <t>242157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299996</t>
+          <t>304769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>349712</t>
+          <t>376472</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>330054</t>
+          <t>357405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>367360</t>
+          <t>397229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6722,32 +6722,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>623101</t>
+          <t>650874</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>586677</t>
+          <t>616162</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>655818</t>
+          <t>687773</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,85%</t>
         </is>
       </c>
     </row>
@@ -6765,32 +6765,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>111331</t>
+          <t>119511</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91072</t>
+          <t>98856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135099</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79017</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6835,32 +6835,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>176781</t>
+          <t>186254</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154456</t>
+          <t>163914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206532</t>
+          <t>213345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -6878,32 +6878,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>13454</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23561</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48771</t>
+          <t>49241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -6991,32 +6991,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>120038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94308</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143329</t>
+          <t>146439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87653</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>73671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103948</t>
+          <t>106552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>204447</t>
+          <t>209863</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179510</t>
+          <t>181421</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>235891</t>
+          <t>238863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -7104,17 +7104,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7174,17 +7174,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7221,32 +7221,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>173086</t>
+          <t>168744</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154412</t>
+          <t>150576</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191528</t>
+          <t>185601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7256,32 +7256,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>235411</t>
+          <t>242111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>220430</t>
+          <t>227136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249417</t>
+          <t>255767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7291,32 +7291,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>408496</t>
+          <t>410856</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384350</t>
+          <t>387031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>432014</t>
+          <t>430364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -7334,32 +7334,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68747</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54830</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>81129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62009</t>
+          <t>62094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>118242</t>
+          <t>117324</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>102681</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136768</t>
+          <t>134605</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -7447,32 +7447,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7482,67 +7482,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>9056</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>16904</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>8359</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>4065</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>15894</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7560,32 +7560,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70562</t>
+          <t>75247</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>61403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85398</t>
+          <t>91724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7595,32 +7595,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59519</t>
+          <t>59892</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>49155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71563</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7630,32 +7630,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>130081</t>
+          <t>135140</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112960</t>
+          <t>117396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>156112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -7673,17 +7673,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7708,17 +7708,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7743,17 +7743,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7790,32 +7790,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>141486</t>
+          <t>173142</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118117</t>
+          <t>148792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163580</t>
+          <t>197938</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>343958</t>
+          <t>276644</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>307381</t>
+          <t>256686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>395826</t>
+          <t>293630</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>485443</t>
+          <t>449786</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>438072</t>
+          <t>418461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>575518</t>
+          <t>483978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -7903,32 +7903,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94474</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>88120</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>127991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>58190</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34930</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77721</t>
+          <t>77559</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7973,32 +7973,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>152663</t>
+          <t>172525</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111080</t>
+          <t>150199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>196745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -8016,102 +8016,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>9801</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>7557</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>13774</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>11004</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>5888</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>18670</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>6589</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>12072</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>4358</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>15939</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -8129,32 +8129,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>74296</t>
+          <t>89125</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>67672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94243</t>
+          <t>113379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8164,32 +8164,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>66981</t>
+          <t>72666</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40529</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91141</t>
+          <t>92315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8199,32 +8199,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>141277</t>
+          <t>161791</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101947</t>
+          <t>134614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172233</t>
+          <t>191440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -8242,17 +8242,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8277,17 +8277,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8312,17 +8312,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8359,32 +8359,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>130164</t>
+          <t>148848</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>136932</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>138800</t>
+          <t>158632</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8394,27 +8394,27 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170474</t>
+          <t>186211</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162659</t>
+          <t>176085</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178082</t>
+          <t>193932</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8429,32 +8429,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>300638</t>
+          <t>335058</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>286479</t>
+          <t>321774</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>312088</t>
+          <t>347279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -8472,32 +8472,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8507,32 +8507,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8542,32 +8542,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8620,32 +8620,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8655,32 +8655,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -8698,32 +8698,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>39415</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>49348</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8733,32 +8733,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>27955</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8768,32 +8768,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>58075</t>
+          <t>67370</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -8811,17 +8811,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8846,17 +8846,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8881,17 +8881,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>149198</t>
+          <t>150196</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>133508</t>
+          <t>134953</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>165217</t>
+          <t>163982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8963,27 +8963,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>197954</t>
+          <t>203364</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>186447</t>
+          <t>191491</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>207762</t>
+          <t>213161</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -8998,32 +8998,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>347152</t>
+          <t>353560</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>328195</t>
+          <t>334432</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>364889</t>
+          <t>372391</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,68%</t>
         </is>
       </c>
     </row>
@@ -9041,32 +9041,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>35601</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>55009</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9076,32 +9076,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9111,32 +9111,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>56406</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46876</t>
+          <t>45564</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70213</t>
+          <t>68743</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -9154,32 +9154,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16894</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9189,32 +9189,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9224,32 +9224,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10674</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -9267,32 +9267,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>69169</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55540</t>
+          <t>57327</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>81810</t>
+          <t>83291</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9302,32 +9302,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>44682</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55644</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9337,32 +9337,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>112460</t>
+          <t>114150</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>96928</t>
+          <t>98154</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>129663</t>
+          <t>131892</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -9380,17 +9380,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9415,17 +9415,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9497,32 +9497,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>327154</t>
+          <t>383691</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>295970</t>
+          <t>352016</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>356863</t>
+          <t>414447</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9532,32 +9532,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>597719</t>
+          <t>483747</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>509343</t>
+          <t>456213</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>732147</t>
+          <t>508119</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9567,32 +9567,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>924873</t>
+          <t>867438</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>821312</t>
+          <t>828890</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1121744</t>
+          <t>906843</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -9610,32 +9610,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>122914</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>104130</t>
+          <t>121687</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>141819</t>
+          <t>166507</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9645,32 +9645,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>95418</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>131943</t>
+          <t>126155</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9680,32 +9680,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>218332</t>
+          <t>251601</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>138258</t>
+          <t>225896</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>262808</t>
+          <t>281081</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -9723,32 +9723,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>34774</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>53527</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9758,32 +9758,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9793,32 +9793,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>61504</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>45930</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>72107</t>
+          <t>82929</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -9836,32 +9836,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>144920</t>
+          <t>155421</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>121923</t>
+          <t>130375</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>176699</t>
+          <t>182027</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9871,32 +9871,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>128593</t>
+          <t>149649</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>129265</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>178601</t>
+          <t>171238</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9906,32 +9906,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>273513</t>
+          <t>305070</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>174407</t>
+          <t>274081</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>332051</t>
+          <t>339056</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -9949,17 +9949,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9984,17 +9984,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10019,17 +10019,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10066,32 +10066,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>396647</t>
+          <t>472648</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>179355</t>
+          <t>443138</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>549917</t>
+          <t>500289</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10101,32 +10101,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>560524</t>
+          <t>651782</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>539372</t>
+          <t>629319</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>577655</t>
+          <t>673067</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10136,32 +10136,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>957172</t>
+          <t>1124431</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>605592</t>
+          <t>1084741</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1132600</t>
+          <t>1159078</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -10179,32 +10179,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>347229</t>
+          <t>114644</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>130443</t>
+          <t>96337</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>654262</t>
+          <t>133281</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10214,32 +10214,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>56759</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10249,32 +10249,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>385275</t>
+          <t>158885</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>158441</t>
+          <t>136197</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>853817</t>
+          <t>180420</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10327,32 +10327,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10362,32 +10362,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -10405,32 +10405,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>182912</t>
+          <t>208526</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>82938</t>
+          <t>180723</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>259170</t>
+          <t>234183</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10440,32 +10440,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>110143</t>
+          <t>125254</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>93913</t>
+          <t>105979</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>144455</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10475,32 +10475,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>293055</t>
+          <t>333780</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>178429</t>
+          <t>304718</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>353961</t>
+          <t>371596</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -10518,17 +10518,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10553,17 +10553,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10588,17 +10588,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10635,32 +10635,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1770672</t>
+          <t>1964205</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1312916</t>
+          <t>1900089</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1930270</t>
+          <t>2028033</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10670,32 +10670,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2668268</t>
+          <t>2657623</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2577228</t>
+          <t>2611447</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2847425</t>
+          <t>2708244</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10705,32 +10705,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4438940</t>
+          <t>4621828</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3958696</t>
+          <t>4541527</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4683345</t>
+          <t>4710838</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -10748,32 +10748,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>852438</t>
+          <t>663408</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>641386</t>
+          <t>618433</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1477012</t>
+          <t>708368</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10783,32 +10783,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>338037</t>
+          <t>366543</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>337336</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>377059</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10818,32 +10818,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1190474</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>950224</t>
+          <t>976529</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1829952</t>
+          <t>1084078</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -10861,32 +10861,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>50492</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>103371</t>
+          <t>103793</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10896,32 +10896,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>86365</t>
+          <t>96077</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10931,32 +10931,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>140722</t>
+          <t>156421</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>112110</t>
+          <t>130668</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>177347</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -10974,32 +10974,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>762156</t>
+          <t>822060</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>600359</t>
+          <t>768890</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>838145</t>
+          <t>882148</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11009,32 +11009,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>583579</t>
+          <t>630481</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>483868</t>
+          <t>590213</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>643754</t>
+          <t>675429</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11044,32 +11044,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1345734</t>
+          <t>1452540</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1165792</t>
+          <t>1381395</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1459122</t>
+          <t>1529462</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -11087,17 +11087,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11122,17 +11122,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11157,17 +11157,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
